--- a/data/source/GSSPs.xlsx
+++ b/data/source/GSSPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nick/work/ics/gssps/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07153CDA-994C-FA4F-BBE9-4E71B46F7727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B28E47A-B152-754D-8CF0-3387C26F1437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38020" yWindow="1740" windowWidth="64000" windowHeight="23540" xr2:uid="{F92FB3CB-5B69-1A4A-BA74-80C42D1E9787}"/>
   </bookViews>
@@ -5177,15 +5177,15 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="59.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="41.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="47.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="32.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="35.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.1640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="38.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="59.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="41.5" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="47.6640625" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="32.83203125" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="35.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="26.1640625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="38.6640625" style="1" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="42.6640625" style="1" customWidth="1"/>
     <col min="12" max="12" width="78.83203125" style="1" customWidth="1"/>
     <col min="13" max="16384" width="10.83203125" style="1"/>
@@ -7648,7 +7648,7 @@
       </c>
     </row>
     <row r="79" spans="1:12" ht="153" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="3" t="s">
         <v>815</v>
       </c>
       <c r="B79" s="12" t="s">
@@ -8926,6 +8926,7 @@
     <hyperlink ref="K9" r:id="rId169" xr:uid="{78D66C0E-653B-9B49-A927-4AD599CEFFCB}"/>
     <hyperlink ref="A4" r:id="rId170" xr:uid="{E058F2CC-26C4-9342-8C01-F213B860CDA2}"/>
     <hyperlink ref="A35" r:id="rId171" xr:uid="{6AAE0529-C65A-F04A-9B09-1B476209A52F}"/>
+    <hyperlink ref="A79" r:id="rId172" xr:uid="{E4C73831-F6FE-6C4C-A7A5-6479811F0FA3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/data/source/GSSPs.xlsx
+++ b/data/source/GSSPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nick/work/ics/gssps/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFF41A9-B263-EF4E-A2BA-9725494D4376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F2D173-2B96-E34F-B17D-430B64EA19E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="660" windowWidth="28680" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="873">
   <si>
     <t>Type</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>https://data.stratigraphy.org/data/gssps/Meghalayan</t>
-  </si>
-  <si>
-    <t>ratified</t>
   </si>
   <si>
     <t>Mawmluh Cave, Meghalaya, India</t>
@@ -140,16 +137,10 @@
     <t>https://data.stratigraphy.org/data/gssps/UpperPleistocene</t>
   </si>
   <si>
-    <t>proposed</t>
-  </si>
-  <si>
     <t>https://stratigraphy.org/gssps/upper-pleistocene</t>
   </si>
   <si>
     <t>GSSP not presently defined</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>Provisionally climatic – Marine Isotope Substage 5e</t>
@@ -5129,6 +5120,15 @@
   </si>
   <si>
     <t>25.262222°N 91.7150°E</t>
+  </si>
+  <si>
+    <t>RatificationNote</t>
+  </si>
+  <si>
+    <t>Proposed</t>
+  </si>
+  <si>
+    <t>Ratified</t>
   </si>
 </sst>
 </file>
@@ -5533,7 +5533,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>3</v>
+        <v>870</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>9</v>
@@ -5553,35 +5553,35 @@
         <v>13</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>869</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -5589,38 +5589,38 @@
         <v>12</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="J3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="68" x14ac:dyDescent="0.2">
@@ -5628,38 +5628,38 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="L4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="M4" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -5667,34 +5667,30 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>871</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>772</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="G5" s="10"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="J5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="K5" s="10" t="s">
         <v>37</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>40</v>
       </c>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
@@ -5704,76 +5700,76 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>781</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="J6" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="K6" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="M6" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="4" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" s="13" t="s">
         <v>52</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="M7" s="8"/>
     </row>
@@ -5782,40 +5778,40 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>693</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="14" t="s">
+      <c r="H8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="I8" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="J8" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="K8" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="M8" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="102" x14ac:dyDescent="0.2">
@@ -5823,40 +5819,40 @@
         <v>12</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="I9" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="J9" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="K9" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="L9" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -5864,38 +5860,38 @@
         <v>12</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="H10" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="I10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="J10" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="K10" s="15" t="s">
         <v>78</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>81</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -5903,38 +5899,38 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="I11" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="J11" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="K11" s="15" t="s">
         <v>87</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>90</v>
       </c>
       <c r="L11" s="7"/>
       <c r="M11" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="68" x14ac:dyDescent="0.2">
@@ -5942,38 +5938,38 @@
         <v>12</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>739</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="I12" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="15" t="s">
         <v>94</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>799</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>97</v>
       </c>
       <c r="L12" s="7"/>
       <c r="M12" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -5981,38 +5977,38 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="I13" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="J13" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="K13" s="15" t="s">
         <v>102</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>800</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>105</v>
       </c>
       <c r="L13" s="7"/>
       <c r="M13" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="68" x14ac:dyDescent="0.2">
@@ -6020,38 +6016,38 @@
         <v>12</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>761</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="7" t="s">
+      <c r="H14" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="I14" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="J14" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="K14" s="15" t="s">
         <v>110</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>801</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>113</v>
       </c>
       <c r="L14" s="7"/>
       <c r="M14" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -6059,35 +6055,35 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="J15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="L15" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>121</v>
       </c>
       <c r="M15" s="7"/>
     </row>
@@ -6096,22 +6092,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G16" s="10"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
@@ -6123,38 +6119,38 @@
         <v>12</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>683</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="I17" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="J17" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="K17" s="15" t="s">
         <v>127</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>803</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>130</v>
       </c>
       <c r="L17" s="7"/>
       <c r="M17" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -6162,37 +6158,37 @@
         <v>12</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>704</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="H18" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="J18" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="K18" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>861</v>
-      </c>
-      <c r="I18" s="7" t="s">
+      <c r="L18" s="7" t="s">
         <v>136</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>139</v>
       </c>
       <c r="M18" s="7"/>
     </row>
@@ -6201,38 +6197,38 @@
         <v>12</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>755</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="7" t="s">
+      <c r="H19" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="I19" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="J19" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="K19" s="15" t="s">
         <v>143</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>804</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>146</v>
       </c>
       <c r="L19" s="7"/>
       <c r="M19" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="102" x14ac:dyDescent="0.2">
@@ -6240,37 +6236,37 @@
         <v>12</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>751</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="I20" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K20" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="L20" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>805</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>154</v>
       </c>
       <c r="M20" s="7"/>
     </row>
@@ -6279,22 +6275,22 @@
         <v>12</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
@@ -6306,38 +6302,38 @@
         <v>12</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G22" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>736</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="7" t="s">
+      <c r="H22" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="I22" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="J22" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="K22" s="15" t="s">
         <v>161</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>164</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -6345,40 +6341,40 @@
         <v>12</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>779</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="7" t="s">
+      <c r="H23" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="I23" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="J23" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="K23" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="L23" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="M23" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -6386,38 +6382,38 @@
         <v>12</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G24" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>765</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="7" t="s">
+      <c r="H24" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="I24" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="J24" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="K24" s="15" t="s">
         <v>179</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>182</v>
       </c>
       <c r="L24" s="7"/>
       <c r="M24" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -6425,38 +6421,38 @@
         <v>12</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>759</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G25" s="10" t="s">
+      <c r="J25" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="H25" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>181</v>
-      </c>
       <c r="K25" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L25" s="7"/>
       <c r="M25" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -6464,38 +6460,38 @@
         <v>12</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="7" t="s">
+      <c r="H26" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="I26" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="J26" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="K26" s="15" t="s">
         <v>192</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>195</v>
       </c>
       <c r="L26" s="7"/>
       <c r="M26" s="14" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="85" x14ac:dyDescent="0.2">
@@ -6503,38 +6499,38 @@
         <v>12</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>737</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="7" t="s">
+      <c r="H27" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="I27" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="J27" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="K27" s="15" t="s">
         <v>200</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>807</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>203</v>
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6542,40 +6538,40 @@
         <v>12</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>699</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="7" t="s">
+      <c r="H28" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="I28" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="J28" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="K28" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="L28" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="M28" s="7" t="s">
         <v>211</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -6583,38 +6579,38 @@
         <v>12</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>755</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="7" t="s">
+      <c r="H29" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="I29" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="J29" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="K29" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>808</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>221</v>
       </c>
       <c r="L29" s="7"/>
       <c r="M29" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -6622,40 +6618,40 @@
         <v>12</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>705</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="7" t="s">
+      <c r="H30" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="I30" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="J30" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="K30" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="L30" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="I30" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="J30" s="10" t="s">
+      <c r="M30" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="M30" s="7" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -6663,38 +6659,38 @@
         <v>12</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>768</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="7" t="s">
+      <c r="H31" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="I31" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="K31" s="15" t="s">
         <v>234</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>237</v>
       </c>
       <c r="L31" s="7"/>
       <c r="M31" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6702,38 +6698,38 @@
         <v>12</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G32" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>702</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="7" t="s">
+      <c r="H32" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="I32" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="J32" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="K32" s="15" t="s">
         <v>242</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>245</v>
       </c>
       <c r="L32" s="7"/>
       <c r="M32" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -6741,35 +6737,35 @@
         <v>12</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="K33" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="L33" s="7" t="s">
         <v>249</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="M33" s="7"/>
     </row>
@@ -6778,22 +6774,22 @@
         <v>12</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G34" s="10"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
@@ -6805,35 +6801,35 @@
         <v>12</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="L35" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>260</v>
       </c>
       <c r="M35" s="7"/>
     </row>
@@ -6842,35 +6838,35 @@
         <v>12</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J36" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="K36" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="L36" s="7" t="s">
         <v>264</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>815</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="K36" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>267</v>
       </c>
       <c r="M36" s="7"/>
     </row>
@@ -6879,22 +6875,22 @@
         <v>12</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G37" s="10"/>
       <c r="H37" s="7"/>
       <c r="I37" s="7" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
@@ -6906,20 +6902,20 @@
         <v>12</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="10"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
@@ -6931,22 +6927,22 @@
         <v>12</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
@@ -6958,33 +6954,33 @@
         <v>12</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H40" s="7"/>
       <c r="I40" s="7" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="M40" s="7"/>
     </row>
@@ -6993,22 +6989,22 @@
         <v>12</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G41" s="10"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
@@ -7020,22 +7016,22 @@
         <v>12</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G42" s="10"/>
       <c r="H42" s="7"/>
       <c r="I42" s="7" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
@@ -7047,34 +7043,34 @@
         <v>12</v>
       </c>
       <c r="B43" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="C43" s="7" t="s">
-        <v>690</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="7" t="s">
+      <c r="H43" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="I43" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="K43" s="15" t="s">
         <v>284</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>822</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="K43" s="15" t="s">
-        <v>287</v>
       </c>
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
@@ -7084,34 +7080,34 @@
         <v>12</v>
       </c>
       <c r="B44" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G44" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="C44" s="7" t="s">
-        <v>686</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" s="7" t="s">
+      <c r="H44" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="I44" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="K44" s="15" t="s">
         <v>290</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="J44" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="K44" s="15" t="s">
-        <v>293</v>
       </c>
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
@@ -7121,34 +7117,34 @@
         <v>12</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>678</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" s="7" t="s">
+      <c r="H45" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="I45" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K45" s="15" t="s">
         <v>296</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>824</v>
-      </c>
-      <c r="J45" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="K45" s="15" t="s">
-        <v>299</v>
       </c>
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
@@ -7158,38 +7154,38 @@
         <v>12</v>
       </c>
       <c r="B46" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G46" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>767</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E46" s="7" t="s">
+      <c r="H46" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="I46" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="J46" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="K46" s="15" t="s">
         <v>303</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>825</v>
-      </c>
-      <c r="J46" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="K46" s="15" t="s">
-        <v>306</v>
       </c>
       <c r="L46" s="7"/>
       <c r="M46" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -7197,38 +7193,38 @@
         <v>12</v>
       </c>
       <c r="B47" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>749</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" s="7" t="s">
+      <c r="H47" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="I47" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="J47" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="K47" s="15" t="s">
         <v>311</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>826</v>
-      </c>
-      <c r="J47" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>314</v>
       </c>
       <c r="L47" s="7"/>
       <c r="M47" s="7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -7236,38 +7232,38 @@
         <v>12</v>
       </c>
       <c r="B48" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G48" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="C48" s="7" t="s">
-        <v>763</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48" s="7" t="s">
+      <c r="H48" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="I48" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K48" s="15" t="s">
         <v>318</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>827</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="K48" s="15" t="s">
-        <v>321</v>
       </c>
       <c r="L48" s="7"/>
       <c r="M48" s="7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -7275,38 +7271,38 @@
         <v>12</v>
       </c>
       <c r="B49" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="C49" s="7" t="s">
-        <v>723</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="7" t="s">
+      <c r="H49" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="I49" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="J49" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="K49" s="15" t="s">
         <v>326</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>828</v>
-      </c>
-      <c r="J49" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="K49" s="15" t="s">
-        <v>329</v>
       </c>
       <c r="L49" s="7"/>
       <c r="M49" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="68" x14ac:dyDescent="0.2">
@@ -7314,22 +7310,22 @@
         <v>12</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G50" s="10"/>
       <c r="H50" s="7"/>
       <c r="I50" s="7" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
@@ -7341,22 +7337,22 @@
         <v>12</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E51" s="7"/>
       <c r="F51" s="7" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G51" s="10"/>
       <c r="H51" s="7"/>
       <c r="I51" s="7" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
@@ -7368,34 +7364,34 @@
         <v>12</v>
       </c>
       <c r="B52" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="G52" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="C52" s="7" t="s">
-        <v>701</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" s="7" t="s">
+      <c r="H52" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="I52" s="7" t="s">
+        <v>828</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="K52" s="15" t="s">
         <v>337</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>831</v>
-      </c>
-      <c r="J52" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="K52" s="15" t="s">
-        <v>340</v>
       </c>
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
@@ -7405,34 +7401,34 @@
         <v>12</v>
       </c>
       <c r="B53" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="C53" s="7" t="s">
-        <v>732</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="7" t="s">
+      <c r="H53" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="I53" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="K53" s="15" t="s">
         <v>343</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>832</v>
-      </c>
-      <c r="J53" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="K53" s="15" t="s">
-        <v>346</v>
       </c>
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
@@ -7442,32 +7438,32 @@
         <v>12</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>859</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="J54" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="K54" s="10" t="s">
         <v>349</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>862</v>
-      </c>
-      <c r="I54" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="J54" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="K54" s="10" t="s">
-        <v>352</v>
       </c>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
@@ -7477,32 +7473,32 @@
         <v>12</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E55" s="7"/>
       <c r="F55" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="I55" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="J55" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="K55" s="10" t="s">
         <v>355</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="J55" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="K55" s="10" t="s">
-        <v>358</v>
       </c>
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
@@ -7512,38 +7508,38 @@
         <v>12</v>
       </c>
       <c r="B56" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="G56" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="C56" s="7" t="s">
-        <v>726</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="7" t="s">
+      <c r="H56" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="I56" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="J56" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K56" s="15" t="s">
         <v>362</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="K56" s="15" t="s">
-        <v>365</v>
       </c>
       <c r="L56" s="7"/>
       <c r="M56" s="9" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7551,38 +7547,38 @@
         <v>12</v>
       </c>
       <c r="B57" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="H57" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="C57" s="7" t="s">
-        <v>703</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="7" t="s">
+      <c r="I57" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="F57" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="J57" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="K57" s="15" t="s">
         <v>369</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="K57" s="15" t="s">
-        <v>372</v>
       </c>
       <c r="L57" s="7"/>
       <c r="M57" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7590,40 +7586,40 @@
         <v>12</v>
       </c>
       <c r="B58" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="G58" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="C58" s="7" t="s">
-        <v>776</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="7" t="s">
+      <c r="H58" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="I58" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="J58" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="H58" s="7" t="s">
+      <c r="K58" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="I58" s="7" t="s">
+      <c r="L58" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="J58" s="10" t="s">
+      <c r="M58" s="7" t="s">
         <v>380</v>
-      </c>
-      <c r="K58" s="15" t="s">
-        <v>381</v>
-      </c>
-      <c r="L58" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="M58" s="7" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7631,40 +7627,40 @@
         <v>12</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="G59" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="C59" s="7" t="s">
-        <v>700</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="7" t="s">
+      <c r="H59" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="I59" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G59" s="10" t="s">
+      <c r="J59" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K59" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="H59" s="7" t="s">
+      <c r="L59" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="I59" s="7" t="s">
+      <c r="M59" s="7" t="s">
         <v>389</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="K59" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="L59" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="M59" s="7" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="68" x14ac:dyDescent="0.2">
@@ -7672,40 +7668,40 @@
         <v>12</v>
       </c>
       <c r="B60" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="G60" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="C60" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="7" t="s">
+      <c r="H60" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="I60" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="J60" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K60" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="H60" s="7" t="s">
+      <c r="L60" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="I60" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="J60" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="K60" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="L60" s="7" t="s">
-        <v>400</v>
-      </c>
       <c r="M60" s="7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -7713,40 +7709,40 @@
         <v>12</v>
       </c>
       <c r="B61" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="C61" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="7" t="s">
+      <c r="H61" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="I61" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="G61" s="10" t="s">
+      <c r="J61" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K61" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="H61" s="7" t="s">
+      <c r="L61" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="I61" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="K61" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="L61" s="7" t="s">
-        <v>408</v>
-      </c>
       <c r="M61" s="7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -7754,22 +7750,22 @@
         <v>12</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="7" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G62" s="10"/>
       <c r="H62" s="7"/>
       <c r="J62" s="10" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="K62" s="10"/>
       <c r="L62" s="7"/>
@@ -7780,37 +7776,37 @@
         <v>12</v>
       </c>
       <c r="B63" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>681</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="C63" s="7" t="s">
-        <v>684</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="7" t="s">
+      <c r="H63" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="I63" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="J63" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="K63" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="H63" s="7" t="s">
+      <c r="L63" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="I63" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="J63" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="K63" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="L63" s="7" t="s">
-        <v>419</v>
       </c>
       <c r="M63" s="7"/>
     </row>
@@ -7819,37 +7815,37 @@
         <v>12</v>
       </c>
       <c r="B64" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="G64" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="C64" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="7" t="s">
+      <c r="H64" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="I64" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="G64" s="10" t="s">
+      <c r="J64" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K64" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="H64" s="7" t="s">
+      <c r="L64" s="7" t="s">
         <v>424</v>
-      </c>
-      <c r="I64" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="J64" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K64" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="L64" s="7" t="s">
-        <v>427</v>
       </c>
       <c r="M64" s="7"/>
     </row>
@@ -7858,38 +7854,38 @@
         <v>12</v>
       </c>
       <c r="B65" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G65" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="C65" s="7" t="s">
-        <v>685</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" s="7" t="s">
+      <c r="H65" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="I65" s="7" t="s">
+        <v>795</v>
+      </c>
+      <c r="J65" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="K65" s="15" t="s">
         <v>430</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="I65" s="7" t="s">
-        <v>798</v>
-      </c>
-      <c r="J65" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="K65" s="15" t="s">
-        <v>433</v>
       </c>
       <c r="L65" s="7"/>
       <c r="M65" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -7897,22 +7893,22 @@
         <v>12</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G66" s="10"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
@@ -7924,22 +7920,22 @@
         <v>12</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="G67" s="10"/>
       <c r="H67" s="7"/>
       <c r="I67" s="7" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
@@ -7951,22 +7947,22 @@
         <v>12</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G68" s="10"/>
       <c r="H68" s="7"/>
       <c r="I68" s="7" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
@@ -7978,36 +7974,36 @@
         <v>12</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E69" s="7"/>
       <c r="F69" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="I69" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="G69" s="10" t="s">
+      <c r="J69" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="K69" s="15" t="s">
         <v>444</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="I69" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="J69" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="K69" s="15" t="s">
-        <v>447</v>
       </c>
       <c r="L69" s="7"/>
       <c r="M69" s="7" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8015,22 +8011,22 @@
         <v>12</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G70" s="10"/>
       <c r="H70" s="7"/>
       <c r="I70" s="7" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
@@ -8042,36 +8038,36 @@
         <v>12</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="J71" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="K71" s="15" t="s">
         <v>453</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>454</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="I71" s="7" t="s">
-        <v>834</v>
-      </c>
-      <c r="J71" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="K71" s="15" t="s">
-        <v>456</v>
       </c>
       <c r="L71" s="7"/>
       <c r="M71" s="7" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="68" x14ac:dyDescent="0.2">
@@ -8079,36 +8075,36 @@
         <v>12</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="I72" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="G72" s="10" t="s">
+      <c r="J72" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="H72" s="7" t="s">
+      <c r="K72" s="15" t="s">
         <v>461</v>
-      </c>
-      <c r="I72" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="J72" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="K72" s="15" t="s">
-        <v>464</v>
       </c>
       <c r="L72" s="7"/>
       <c r="M72" s="7" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8116,36 +8112,36 @@
         <v>12</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="I73" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="G73" s="10" t="s">
+      <c r="J73" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="H73" s="7" t="s">
+      <c r="K73" s="15" t="s">
         <v>469</v>
-      </c>
-      <c r="I73" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="J73" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="K73" s="15" t="s">
-        <v>472</v>
       </c>
       <c r="L73" s="7"/>
       <c r="M73" s="7" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8153,36 +8149,36 @@
         <v>12</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="I74" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="G74" s="10" t="s">
+      <c r="J74" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="H74" s="7" t="s">
+      <c r="K74" s="15" t="s">
         <v>477</v>
-      </c>
-      <c r="I74" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="J74" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="K74" s="15" t="s">
-        <v>480</v>
       </c>
       <c r="L74" s="7"/>
       <c r="M74" s="9" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -8190,36 +8186,36 @@
         <v>12</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="I75" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="G75" s="10" t="s">
+      <c r="J75" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="H75" s="7" t="s">
+      <c r="K75" s="15" t="s">
         <v>485</v>
-      </c>
-      <c r="I75" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="J75" s="10" t="s">
-        <v>487</v>
-      </c>
-      <c r="K75" s="15" t="s">
-        <v>488</v>
       </c>
       <c r="L75" s="7"/>
       <c r="M75" s="7" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8227,36 +8223,36 @@
         <v>12</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="I76" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="G76" s="10" t="s">
+      <c r="J76" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="H76" s="7" t="s">
+      <c r="K76" s="15" t="s">
         <v>493</v>
-      </c>
-      <c r="I76" s="7" t="s">
-        <v>494</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="K76" s="15" t="s">
-        <v>496</v>
       </c>
       <c r="L76" s="7"/>
       <c r="M76" s="7" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8264,36 +8260,36 @@
         <v>12</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E77" s="7"/>
       <c r="F77" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="I77" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="G77" s="10" t="s">
+      <c r="J77" s="10" t="s">
         <v>500</v>
       </c>
-      <c r="H77" s="7" t="s">
+      <c r="K77" s="15" t="s">
         <v>501</v>
-      </c>
-      <c r="I77" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="J77" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="K77" s="15" t="s">
-        <v>504</v>
       </c>
       <c r="L77" s="7"/>
       <c r="M77" s="7" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -8301,36 +8297,36 @@
         <v>12</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="I78" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="G78" s="10" t="s">
+      <c r="J78" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="H78" s="7" t="s">
+      <c r="K78" s="15" t="s">
         <v>509</v>
-      </c>
-      <c r="I78" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="J78" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="K78" s="15" t="s">
-        <v>512</v>
       </c>
       <c r="L78" s="7"/>
       <c r="M78" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="153" x14ac:dyDescent="0.2">
@@ -8338,35 +8334,35 @@
         <v>12</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="J79" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="G79" s="10" t="s">
+      <c r="K79" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="H79" s="7" t="s">
+      <c r="L79" s="7" t="s">
         <v>517</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>835</v>
-      </c>
-      <c r="J79" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="K79" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="L79" s="7" t="s">
-        <v>520</v>
       </c>
       <c r="M79" s="7"/>
     </row>
@@ -8375,36 +8371,36 @@
         <v>12</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="I80" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="J80" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="G80" s="10" t="s">
+      <c r="K80" s="15" t="s">
         <v>523</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="I80" s="7" t="s">
-        <v>836</v>
-      </c>
-      <c r="J80" s="10" t="s">
-        <v>525</v>
-      </c>
-      <c r="K80" s="15" t="s">
-        <v>526</v>
       </c>
       <c r="L80" s="7"/>
       <c r="M80" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -8412,36 +8408,36 @@
         <v>12</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="J81" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="G81" s="10" t="s">
+      <c r="K81" s="15" t="s">
         <v>530</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="I81" s="7" t="s">
-        <v>837</v>
-      </c>
-      <c r="J81" s="10" t="s">
-        <v>532</v>
-      </c>
-      <c r="K81" s="15" t="s">
-        <v>533</v>
       </c>
       <c r="L81" s="7"/>
       <c r="M81" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8449,36 +8445,36 @@
         <v>12</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="I82" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="J82" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="G82" s="10" t="s">
+      <c r="K82" s="15" t="s">
         <v>530</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="I82" s="7" t="s">
-        <v>838</v>
-      </c>
-      <c r="J82" s="10" t="s">
-        <v>532</v>
-      </c>
-      <c r="K82" s="15" t="s">
-        <v>533</v>
       </c>
       <c r="L82" s="7"/>
       <c r="M82" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -8486,36 +8482,36 @@
         <v>12</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E83" s="7"/>
       <c r="F83" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="J83" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="K83" s="15" t="s">
         <v>538</v>
-      </c>
-      <c r="G83" s="10" t="s">
-        <v>539</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="I83" s="7" t="s">
-        <v>839</v>
-      </c>
-      <c r="J83" s="10" t="s">
-        <v>532</v>
-      </c>
-      <c r="K83" s="15" t="s">
-        <v>541</v>
       </c>
       <c r="L83" s="7"/>
       <c r="M83" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="204" x14ac:dyDescent="0.2">
@@ -8523,36 +8519,36 @@
         <v>12</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="L84" s="7"/>
       <c r="M84" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="102" x14ac:dyDescent="0.2">
@@ -8560,36 +8556,36 @@
         <v>12</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="J85" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="G85" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="I85" s="7" t="s">
-        <v>841</v>
-      </c>
-      <c r="J85" s="7" t="s">
-        <v>550</v>
-      </c>
       <c r="K85" s="7" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="L85" s="7"/>
       <c r="M85" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="102" x14ac:dyDescent="0.2">
@@ -8597,36 +8593,36 @@
         <v>12</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E86" s="7"/>
       <c r="F86" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="I86" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="J86" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="G86" s="10" t="s">
-        <v>553</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="I86" s="7" t="s">
-        <v>842</v>
-      </c>
-      <c r="J86" s="7" t="s">
-        <v>555</v>
-      </c>
       <c r="K86" s="7" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="L86" s="7"/>
       <c r="M86" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8634,36 +8630,36 @@
         <v>12</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="J87" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="K87" s="15" t="s">
         <v>557</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>558</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="I87" s="7" t="s">
-        <v>843</v>
-      </c>
-      <c r="J87" s="10" t="s">
-        <v>525</v>
-      </c>
-      <c r="K87" s="15" t="s">
-        <v>560</v>
       </c>
       <c r="L87" s="7"/>
       <c r="M87" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8671,36 +8667,36 @@
         <v>12</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E88" s="7"/>
       <c r="F88" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="I88" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="J88" s="10" t="s">
         <v>562</v>
       </c>
-      <c r="G88" s="10" t="s">
+      <c r="K88" s="15" t="s">
         <v>563</v>
-      </c>
-      <c r="H88" s="7" t="s">
-        <v>564</v>
-      </c>
-      <c r="I88" s="7" t="s">
-        <v>844</v>
-      </c>
-      <c r="J88" s="10" t="s">
-        <v>565</v>
-      </c>
-      <c r="K88" s="15" t="s">
-        <v>566</v>
       </c>
       <c r="L88" s="7"/>
       <c r="M88" s="9" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8708,36 +8704,36 @@
         <v>12</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="J89" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="K89" s="15" t="s">
         <v>569</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>570</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="I89" s="7" t="s">
-        <v>845</v>
-      </c>
-      <c r="J89" s="10" t="s">
-        <v>565</v>
-      </c>
-      <c r="K89" s="15" t="s">
-        <v>572</v>
       </c>
       <c r="L89" s="7"/>
       <c r="M89" s="9" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8745,36 +8741,36 @@
         <v>12</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E90" s="7"/>
       <c r="F90" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>843</v>
+      </c>
+      <c r="J90" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="K90" s="15" t="s">
         <v>575</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>576</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="I90" s="7" t="s">
-        <v>846</v>
-      </c>
-      <c r="J90" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="K90" s="15" t="s">
-        <v>578</v>
       </c>
       <c r="L90" s="7"/>
       <c r="M90" s="9" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8782,36 +8778,36 @@
         <v>12</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="J91" s="10" t="s">
         <v>581</v>
       </c>
-      <c r="G91" s="10" t="s">
+      <c r="K91" s="15" t="s">
         <v>582</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="I91" s="7" t="s">
-        <v>847</v>
-      </c>
-      <c r="J91" s="10" t="s">
-        <v>584</v>
-      </c>
-      <c r="K91" s="15" t="s">
-        <v>585</v>
       </c>
       <c r="L91" s="7"/>
       <c r="M91" s="9" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -8819,36 +8815,36 @@
         <v>12</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E92" s="7"/>
       <c r="F92" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="L92" s="7"/>
       <c r="M92" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8856,36 +8852,36 @@
         <v>12</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="I93" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="J93" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="K93" s="15" t="s">
         <v>593</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="H93" s="7" t="s">
-        <v>595</v>
-      </c>
-      <c r="I93" s="7" t="s">
-        <v>849</v>
-      </c>
-      <c r="J93" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="K93" s="15" t="s">
-        <v>596</v>
       </c>
       <c r="L93" s="7"/>
       <c r="M93" s="9" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8893,36 +8889,36 @@
         <v>12</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E94" s="7"/>
       <c r="F94" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="I94" s="7" t="s">
         <v>599</v>
       </c>
-      <c r="G94" s="10" t="s">
+      <c r="J94" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K94" s="15" t="s">
         <v>600</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>601</v>
-      </c>
-      <c r="I94" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="J94" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="K94" s="15" t="s">
-        <v>603</v>
       </c>
       <c r="L94" s="7"/>
       <c r="M94" s="9" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -8930,22 +8926,22 @@
         <v>12</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="7" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="G95" s="10"/>
       <c r="H95" s="7"/>
       <c r="I95" s="7" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="J95" s="10"/>
       <c r="K95" s="10"/>
@@ -8957,36 +8953,36 @@
         <v>12</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E96" s="7"/>
       <c r="F96" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="I96" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="J96" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="K96" s="15" t="s">
         <v>608</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>609</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="I96" s="7" t="s">
-        <v>851</v>
-      </c>
-      <c r="J96" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="K96" s="15" t="s">
-        <v>611</v>
       </c>
       <c r="L96" s="7"/>
       <c r="M96" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -8994,36 +8990,36 @@
         <v>12</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="J97" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="K97" s="15" t="s">
         <v>614</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>615</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="I97" s="7" t="s">
-        <v>852</v>
-      </c>
-      <c r="J97" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="K97" s="15" t="s">
-        <v>617</v>
       </c>
       <c r="L97" s="7"/>
       <c r="M97" s="9" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -9031,36 +9027,36 @@
         <v>12</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E98" s="7"/>
       <c r="F98" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="J98" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="K98" s="15" t="s">
         <v>620</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="I98" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="J98" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="K98" s="15" t="s">
-        <v>623</v>
       </c>
       <c r="L98" s="7"/>
       <c r="M98" s="9" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="68" x14ac:dyDescent="0.2">
@@ -9068,36 +9064,36 @@
         <v>12</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="J99" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="K99" s="15" t="s">
         <v>626</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>628</v>
-      </c>
-      <c r="I99" s="7" t="s">
-        <v>854</v>
-      </c>
-      <c r="J99" s="10" t="s">
-        <v>565</v>
-      </c>
-      <c r="K99" s="15" t="s">
-        <v>629</v>
       </c>
       <c r="L99" s="7"/>
       <c r="M99" s="9" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="34" x14ac:dyDescent="0.2">
@@ -9105,22 +9101,22 @@
         <v>12</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E100" s="7"/>
       <c r="F100" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G100" s="10"/>
       <c r="H100" s="7"/>
       <c r="I100" s="7" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="J100" s="10"/>
       <c r="K100" s="10"/>
@@ -9132,20 +9128,20 @@
         <v>12</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="7"/>
       <c r="G101" s="10"/>
       <c r="H101" s="7"/>
       <c r="I101" s="7" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="J101" s="10"/>
       <c r="K101" s="10"/>
@@ -9157,20 +9153,20 @@
         <v>12</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="7"/>
       <c r="G102" s="10"/>
       <c r="H102" s="7"/>
       <c r="I102" s="7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="J102" s="10"/>
       <c r="K102" s="10"/>
@@ -9182,20 +9178,20 @@
         <v>12</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="7"/>
       <c r="G103" s="10"/>
       <c r="H103" s="7"/>
       <c r="I103" s="7" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="J103" s="10"/>
       <c r="K103" s="10"/>
@@ -9207,36 +9203,36 @@
         <v>12</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E104" s="7"/>
       <c r="F104" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="I104" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="J104" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="K104" s="15" t="s">
         <v>639</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>640</v>
-      </c>
-      <c r="H104" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="I104" s="7" t="s">
-        <v>857</v>
-      </c>
-      <c r="J104" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="K104" s="15" t="s">
-        <v>642</v>
       </c>
       <c r="L104" s="7"/>
       <c r="M104" s="9" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="85" x14ac:dyDescent="0.2">
@@ -9244,36 +9240,36 @@
         <v>12</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="I105" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="G105" s="10" t="s">
+      <c r="J105" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="K105" s="15" t="s">
         <v>646</v>
-      </c>
-      <c r="H105" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="I105" s="7" t="s">
-        <v>648</v>
-      </c>
-      <c r="J105" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="K105" s="15" t="s">
-        <v>649</v>
       </c>
       <c r="L105" s="7"/>
       <c r="M105" s="9" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="51" x14ac:dyDescent="0.2">
@@ -9281,402 +9277,402 @@
         <v>12</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="G106" s="10"/>
       <c r="H106" s="7"/>
       <c r="J106" s="10"/>
       <c r="K106" s="15" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="L106" s="7"/>
       <c r="M106" s="7"/>
     </row>
     <row r="107" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A107" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G107" s="10"/>
       <c r="H107" s="7"/>
       <c r="J107" s="10" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="L107" s="7"/>
       <c r="M107" s="7"/>
     </row>
     <row r="108" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A108" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="B108" s="7" t="s">
         <v>654</v>
       </c>
-      <c r="B108" s="7" t="s">
-        <v>657</v>
-      </c>
       <c r="C108" s="7" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E108" s="7"/>
       <c r="F108" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G108" s="10"/>
       <c r="H108" s="7"/>
       <c r="J108" s="10" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
     </row>
     <row r="109" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A109" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E109" s="7"/>
       <c r="F109" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G109" s="10"/>
       <c r="H109" s="7"/>
       <c r="J109" s="10" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
     </row>
     <row r="110" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A110" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E110" s="7"/>
       <c r="F110" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G110" s="10"/>
       <c r="H110" s="7"/>
       <c r="J110" s="10" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
     </row>
     <row r="111" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A111" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G111" s="10"/>
       <c r="H111" s="7"/>
       <c r="J111" s="10" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
     </row>
     <row r="112" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A112" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G112" s="10"/>
       <c r="H112" s="7"/>
       <c r="J112" s="10" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
     </row>
     <row r="113" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A113" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E113" s="7"/>
       <c r="F113" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G113" s="10"/>
       <c r="H113" s="7"/>
       <c r="J113" s="10" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="L113" s="7"/>
       <c r="M113" s="7"/>
     </row>
     <row r="114" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E114" s="7"/>
       <c r="F114" s="7" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G114" s="10"/>
       <c r="H114" s="7"/>
       <c r="J114" s="10" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="L114" s="7"/>
       <c r="M114" s="7"/>
     </row>
     <row r="115" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E115" s="7"/>
       <c r="F115" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G115" s="10"/>
       <c r="H115" s="7"/>
       <c r="J115" s="10" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="K115" s="10" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="L115" s="7"/>
       <c r="M115" s="7"/>
     </row>
     <row r="116" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E116" s="7"/>
       <c r="F116" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G116" s="10"/>
       <c r="H116" s="7"/>
       <c r="J116" s="10" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="K116" s="10" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="L116" s="7"/>
       <c r="M116" s="7"/>
     </row>
     <row r="117" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A117" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>34</v>
+        <v>871</v>
       </c>
       <c r="E117" s="7"/>
       <c r="F117" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G117" s="10"/>
       <c r="H117" s="7"/>
       <c r="J117" s="10" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="K117" s="10" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="L117" s="7"/>
       <c r="M117" s="7"/>
     </row>
     <row r="118" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A118" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="2" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="G118" s="10" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="H118" s="7" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="L118" s="7"/>
       <c r="M118" s="7"/>
     </row>
     <row r="119" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A119" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="E119" s="7"/>
       <c r="F119" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="G119" s="10"/>
       <c r="H119" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="I119" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="J119" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="K119" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="L119" s="9" t="s">
         <v>674</v>
-      </c>
-      <c r="I119" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="J119" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="K119" s="15" t="s">
-        <v>676</v>
-      </c>
-      <c r="L119" s="9" t="s">
-        <v>677</v>
       </c>
       <c r="M119" s="7"/>
     </row>
@@ -9796,482 +9792,482 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B1" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B3" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B4" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B5" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B7" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B8" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B9" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B10" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B12" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B13" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B14" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B17" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B18" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B19" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B20" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B21" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B22" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B23" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B24" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B26" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B28" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B30" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B31" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B32" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B33" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B34" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B35" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B36" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B37" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B38" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B40" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B41" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B43" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B44" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B45" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B47" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B48" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B50" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B51" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B52" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B53" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B54" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B55" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B56" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B57" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B58" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B59" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B60" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
@@ -10279,327 +10275,327 @@
         <v>13</v>
       </c>
       <c r="B61" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B62" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B63" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B64" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B65" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B66" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B67" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B68" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B69" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B71" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B72" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B73" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B74" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B75" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B76" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B77" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B78" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B79" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B80" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B81" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B82" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B83" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B84" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B85" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B86" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B87" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B88" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B89" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B90" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B91" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B92" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B93" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B94" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B95" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B96" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B97" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B98" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B99" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B100" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B101" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/GSSPs.xlsx
+++ b/data/source/GSSPs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nick/work/ics/gssps/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F2D173-2B96-E34F-B17D-430B64EA19E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98538A69-A928-ED47-8E2E-4B72FA930839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="660" windowWidth="28680" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1800" yWindow="660" windowWidth="28680" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GSSPs" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
     <t>IRI</t>
   </si>
   <si>
-    <t>stratotypeOf</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -5129,6 +5126,9 @@
   </si>
   <si>
     <t>Ratified</t>
+  </si>
+  <si>
+    <t>representsBoundary</t>
   </si>
 </sst>
 </file>
@@ -5226,7 +5226,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -5246,32 +5246,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -5496,7 +5489,7 @@
     <col min="6" max="6" width="47.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="19.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="32.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="35.33203125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="35.33203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="26.1640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="38.6640625" style="1" customWidth="1"/>
     <col min="12" max="12" width="42.6640625" style="1" customWidth="1"/>
@@ -5512,4169 +5505,3909 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="45.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="5" t="s">
+      <c r="E5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="I5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="45.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="4" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>869</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="7" t="s">
+      <c r="D12" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="I16" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="8"/>
+      <c r="I21" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+    </row>
+    <row r="22" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="M26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G34" s="8"/>
+      <c r="I34" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+    </row>
+    <row r="35" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G37" s="8"/>
+      <c r="I37" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+    </row>
+    <row r="38" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="G38" s="8"/>
+      <c r="I38" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+    </row>
+    <row r="39" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G39" s="8"/>
+      <c r="I39" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+    </row>
+    <row r="40" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G41" s="8"/>
+      <c r="I41" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+    </row>
+    <row r="42" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G42" s="8"/>
+      <c r="I42" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+    </row>
+    <row r="43" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K43" s="12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K45" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="K46" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="K47" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="K49" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G50" s="8"/>
+      <c r="I50" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+    </row>
+    <row r="51" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G51" s="8"/>
+      <c r="I51" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+    </row>
+    <row r="52" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K52" s="12" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="136" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="K53" s="12" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="K56" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="M56" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="K57" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="K58" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="K59" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="K60" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="K61" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="G62" s="8"/>
+      <c r="J62" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="K62" s="8"/>
+    </row>
+    <row r="63" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="K63" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="J64" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>741</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="K64" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="K65" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G66" s="8"/>
+      <c r="I66" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+    </row>
+    <row r="67" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="G67" s="8"/>
+      <c r="I67" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+    </row>
+    <row r="68" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G68" s="8"/>
+      <c r="I68" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+    </row>
+    <row r="69" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="K69" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="G70" s="8"/>
+      <c r="I70" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+    </row>
+    <row r="71" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K71" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K72" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="K73" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="K74" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="M74" s="7" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="K75" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="K76" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="K77" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="J78" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="K78" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="J79" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="J80" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="K80" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="J81" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="K81" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="K82" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="J83" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="K83" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="204" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="J84" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="K84" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="J87" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="K87" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="K88" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="M88" s="7" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="J89" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="K89" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="M89" s="7" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="K90" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="M90" s="7" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="K91" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="M91" s="7" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="K93" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="M93" s="7" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="J94" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K94" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="M94" s="7" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="G95" s="8"/>
+      <c r="I95" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+    </row>
+    <row r="96" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="J96" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="K96" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="J97" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="K97" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="M97" s="7" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>769</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="D98" s="6" t="s">
         <v>871</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-    </row>
-    <row r="6" spans="1:13" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="4" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>868</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>778</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8" t="s">
+      <c r="F98" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="J98" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K98" s="12" t="s">
+        <v>619</v>
+      </c>
+      <c r="M98" s="7" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="J99" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="K99" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="M99" s="7" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="G100" s="8"/>
+      <c r="I100" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+    </row>
+    <row r="101" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="G101" s="8"/>
+      <c r="I101" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+    </row>
+    <row r="102" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="G102" s="8"/>
+      <c r="I102" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
+    </row>
+    <row r="103" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="G103" s="8"/>
+      <c r="I103" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="J103" s="8"/>
+      <c r="K103" s="8"/>
+    </row>
+    <row r="104" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="J104" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K104" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="M104" s="7" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="J105" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K105" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="M105" s="7" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="G106" s="8"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="12" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G107" s="8"/>
+      <c r="J107" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K107" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G108" s="8"/>
+      <c r="J108" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K108" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G109" s="8"/>
+      <c r="J109" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K109" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G110" s="8"/>
+      <c r="J110" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G111" s="8"/>
+      <c r="J111" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K111" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G112" s="8"/>
+      <c r="J112" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G113" s="8"/>
+      <c r="J113" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K113" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="G114" s="8"/>
+      <c r="J114" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="K114" s="3" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G115" s="8"/>
+      <c r="J115" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="K115" s="8" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G116" s="8"/>
+      <c r="J116" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="K116" s="8" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G117" s="8"/>
+      <c r="J117" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="K117" s="8" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="J118" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="M7" s="8"/>
-    </row>
-    <row r="8" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>690</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>713</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>745</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>777</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>736</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>796</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>765</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>797</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>798</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>730</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>689</v>
-      </c>
-      <c r="D16" s="7" t="s">
+      <c r="K118" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="D119" s="6" t="s">
         <v>871</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7" t="s">
-        <v>799</v>
-      </c>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-    </row>
-    <row r="17" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>680</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>800</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>701</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="M18" s="7"/>
-    </row>
-    <row r="19" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>801</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>802</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="M20" s="7"/>
-    </row>
-    <row r="21" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>685</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7" t="s">
-        <v>803</v>
-      </c>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-    </row>
-    <row r="22" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>733</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>776</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>762</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A26" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>703</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="L26" s="7"/>
-      <c r="M26" s="14" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="85" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>734</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>804</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>696</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="I28" s="7" t="s">
+      <c r="F119" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="G119" s="8"/>
+      <c r="H119" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="J119" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="J28" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>755</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>805</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>702</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>806</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="M30" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>807</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>699</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>808</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A33" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>677</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="M33" s="7"/>
-    </row>
-    <row r="34" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A34" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>679</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-    </row>
-    <row r="35" spans="1:13" ht="85" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>684</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="M35" s="7"/>
-    </row>
-    <row r="36" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A36" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>719</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="K36" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="M36" s="7"/>
-    </row>
-    <row r="37" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A37" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="G37" s="10"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7" t="s">
-        <v>813</v>
-      </c>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-    </row>
-    <row r="38" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>688</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-    </row>
-    <row r="39" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A39" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>763</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="G39" s="10"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7" t="s">
-        <v>815</v>
-      </c>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-    </row>
-    <row r="40" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A40" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>727</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7" t="s">
-        <v>816</v>
-      </c>
-      <c r="J40" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="K40" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="L40" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="M40" s="7"/>
-    </row>
-    <row r="41" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A41" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>743</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="G41" s="10"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7" t="s">
-        <v>817</v>
-      </c>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-    </row>
-    <row r="42" spans="1:13" ht="85" x14ac:dyDescent="0.2">
-      <c r="A42" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>691</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G42" s="10"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7" t="s">
-        <v>818</v>
-      </c>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-    </row>
-    <row r="43" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A43" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>687</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>819</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="K43" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-    </row>
-    <row r="44" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A44" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>683</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>820</v>
-      </c>
-      <c r="J44" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="K44" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-    </row>
-    <row r="45" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A45" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>821</v>
-      </c>
-      <c r="J45" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K45" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-    </row>
-    <row r="46" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A46" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>764</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>822</v>
-      </c>
-      <c r="J46" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="K46" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A47" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="J47" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A48" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>760</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>824</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K48" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A49" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>720</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>825</v>
-      </c>
-      <c r="J49" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="K49" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A50" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>749</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="G50" s="10"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7" t="s">
-        <v>826</v>
-      </c>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-    </row>
-    <row r="51" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A51" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>740</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="G51" s="10"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7" t="s">
-        <v>827</v>
-      </c>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-    </row>
-    <row r="52" spans="1:13" ht="85" x14ac:dyDescent="0.2">
-      <c r="A52" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>698</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>828</v>
-      </c>
-      <c r="J52" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="K52" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-    </row>
-    <row r="53" spans="1:13" ht="136" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>729</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>829</v>
-      </c>
-      <c r="J53" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="K53" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-    </row>
-    <row r="54" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>678</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>859</v>
-      </c>
-      <c r="I54" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="J54" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="K54" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-    </row>
-    <row r="55" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>742</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="J55" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="K55" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-    </row>
-    <row r="56" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>723</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="K56" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="L56" s="7"/>
-      <c r="M56" s="9" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>700</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="K57" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="L57" s="7"/>
-      <c r="M57" s="7" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>773</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="I58" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="J58" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="K58" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="L58" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="M58" s="7" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>697</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="K59" s="15" t="s">
-        <v>387</v>
-      </c>
-      <c r="L59" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="M59" s="7" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A60" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>772</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="J60" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="K60" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="L60" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="M60" s="7" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A61" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>751</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="K61" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="L61" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="M61" s="7" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A62" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>728</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="G62" s="10"/>
-      <c r="H62" s="7"/>
-      <c r="J62" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="K62" s="10"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
-    </row>
-    <row r="63" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A63" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>681</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="I63" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="J63" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="K63" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="L63" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="M63" s="7"/>
-    </row>
-    <row r="64" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>753</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="G64" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="I64" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="J64" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="K64" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="L64" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="M64" s="7"/>
-    </row>
-    <row r="65" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A65" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>682</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="I65" s="7" t="s">
-        <v>795</v>
-      </c>
-      <c r="J65" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="K65" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="L65" s="7"/>
-      <c r="M65" s="7" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A66" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>718</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="G66" s="10"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="7"/>
-      <c r="M66" s="7"/>
-    </row>
-    <row r="67" spans="1:13" ht="119" x14ac:dyDescent="0.2">
-      <c r="A67" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>725</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="G67" s="10"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7" t="s">
-        <v>830</v>
-      </c>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="7"/>
-      <c r="M67" s="7"/>
-    </row>
-    <row r="68" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A68" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>739</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="G68" s="10"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
-    </row>
-    <row r="69" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A69" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>686</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="G69" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="I69" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="J69" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="K69" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="L69" s="7"/>
-      <c r="M69" s="7" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A70" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="G70" s="10"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="J70" s="10"/>
-      <c r="K70" s="10"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
-    </row>
-    <row r="71" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A71" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="I71" s="7" t="s">
-        <v>831</v>
-      </c>
-      <c r="J71" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="K71" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="L71" s="7"/>
-      <c r="M71" s="7" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A72" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>766</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>457</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="I72" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="J72" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K72" s="15" t="s">
-        <v>461</v>
-      </c>
-      <c r="L72" s="7"/>
-      <c r="M72" s="7" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="21.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>709</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="I73" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="J73" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="K73" s="15" t="s">
-        <v>469</v>
-      </c>
-      <c r="L73" s="7"/>
-      <c r="M73" s="7" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A74" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>712</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>473</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="I74" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="J74" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="K74" s="15" t="s">
-        <v>477</v>
-      </c>
-      <c r="L74" s="7"/>
-      <c r="M74" s="9" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A75" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>714</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="H75" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="I75" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="J75" s="10" t="s">
-        <v>484</v>
-      </c>
-      <c r="K75" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="L75" s="7"/>
-      <c r="M75" s="7" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A76" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>707</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="H76" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="I76" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>492</v>
-      </c>
-      <c r="K76" s="15" t="s">
-        <v>493</v>
-      </c>
-      <c r="L76" s="7"/>
-      <c r="M76" s="7" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A77" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>708</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="I77" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="J77" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="K77" s="15" t="s">
-        <v>501</v>
-      </c>
-      <c r="L77" s="7"/>
-      <c r="M77" s="7" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A78" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>747</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="I78" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="J78" s="10" t="s">
-        <v>508</v>
-      </c>
-      <c r="K78" s="15" t="s">
-        <v>509</v>
-      </c>
-      <c r="L78" s="7"/>
-      <c r="M78" s="7" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="153" x14ac:dyDescent="0.2">
-      <c r="A79" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>731</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>832</v>
-      </c>
-      <c r="J79" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="K79" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="L79" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="M79" s="7"/>
-    </row>
-    <row r="80" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A80" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>779</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>520</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="I80" s="7" t="s">
-        <v>833</v>
-      </c>
-      <c r="J80" s="10" t="s">
-        <v>522</v>
-      </c>
-      <c r="K80" s="15" t="s">
-        <v>523</v>
-      </c>
-      <c r="L80" s="7"/>
-      <c r="M80" s="7" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A81" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>732</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="I81" s="7" t="s">
-        <v>834</v>
-      </c>
-      <c r="J81" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="K81" s="15" t="s">
-        <v>530</v>
-      </c>
-      <c r="L81" s="7"/>
-      <c r="M81" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A82" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>715</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="G82" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="I82" s="7" t="s">
-        <v>835</v>
-      </c>
-      <c r="J82" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="K82" s="15" t="s">
-        <v>530</v>
-      </c>
-      <c r="L82" s="7"/>
-      <c r="M82" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A83" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>722</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="G83" s="10" t="s">
-        <v>536</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="I83" s="7" t="s">
-        <v>836</v>
-      </c>
-      <c r="J83" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="K83" s="15" t="s">
-        <v>538</v>
-      </c>
-      <c r="L83" s="7"/>
-      <c r="M83" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="204" x14ac:dyDescent="0.2">
-      <c r="A84" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>759</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="G84" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="H84" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="I84" s="7" t="s">
-        <v>837</v>
-      </c>
-      <c r="J84" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="K84" s="15" t="s">
-        <v>538</v>
-      </c>
-      <c r="L84" s="7"/>
-      <c r="M84" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A85" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>761</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="G85" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="I85" s="7" t="s">
-        <v>838</v>
-      </c>
-      <c r="J85" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="K85" s="7" t="s">
-        <v>860</v>
-      </c>
-      <c r="L85" s="7"/>
-      <c r="M85" s="7" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="102" x14ac:dyDescent="0.2">
-      <c r="A86" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>676</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="G86" s="10" t="s">
-        <v>550</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="I86" s="7" t="s">
-        <v>839</v>
-      </c>
-      <c r="J86" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="K86" s="7" t="s">
-        <v>861</v>
-      </c>
-      <c r="L86" s="7"/>
-      <c r="M86" s="7" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A87" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>555</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>556</v>
-      </c>
-      <c r="I87" s="7" t="s">
-        <v>840</v>
-      </c>
-      <c r="J87" s="10" t="s">
-        <v>522</v>
-      </c>
-      <c r="K87" s="15" t="s">
-        <v>557</v>
-      </c>
-      <c r="L87" s="7"/>
-      <c r="M87" s="7" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A88" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>721</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="H88" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="I88" s="7" t="s">
-        <v>841</v>
-      </c>
-      <c r="J88" s="10" t="s">
-        <v>562</v>
-      </c>
-      <c r="K88" s="15" t="s">
-        <v>563</v>
-      </c>
-      <c r="L88" s="7"/>
-      <c r="M88" s="9" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A89" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>726</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="I89" s="7" t="s">
-        <v>842</v>
-      </c>
-      <c r="J89" s="10" t="s">
-        <v>562</v>
-      </c>
-      <c r="K89" s="15" t="s">
-        <v>569</v>
-      </c>
-      <c r="L89" s="7"/>
-      <c r="M89" s="9" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A90" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>573</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="I90" s="7" t="s">
-        <v>843</v>
-      </c>
-      <c r="J90" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="K90" s="15" t="s">
-        <v>575</v>
-      </c>
-      <c r="L90" s="7"/>
-      <c r="M90" s="9" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A91" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>705</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7" t="s">
-        <v>578</v>
-      </c>
-      <c r="G91" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>580</v>
-      </c>
-      <c r="I91" s="7" t="s">
-        <v>844</v>
-      </c>
-      <c r="J91" s="10" t="s">
-        <v>581</v>
-      </c>
-      <c r="K91" s="15" t="s">
-        <v>582</v>
-      </c>
-      <c r="L91" s="7"/>
-      <c r="M91" s="9" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A92" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>704</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="H92" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="I92" s="7" t="s">
-        <v>845</v>
-      </c>
-      <c r="J92" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>862</v>
-      </c>
-      <c r="L92" s="7"/>
-      <c r="M92" s="7" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A93" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>710</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7" t="s">
-        <v>590</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>591</v>
-      </c>
-      <c r="H93" s="7" t="s">
-        <v>592</v>
-      </c>
-      <c r="I93" s="7" t="s">
-        <v>846</v>
-      </c>
-      <c r="J93" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="K93" s="15" t="s">
-        <v>593</v>
-      </c>
-      <c r="L93" s="7"/>
-      <c r="M93" s="9" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A94" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>595</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>767</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7" t="s">
-        <v>596</v>
-      </c>
-      <c r="G94" s="10" t="s">
-        <v>597</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>598</v>
-      </c>
-      <c r="I94" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="J94" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K94" s="15" t="s">
-        <v>600</v>
-      </c>
-      <c r="L94" s="7"/>
-      <c r="M94" s="9" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A95" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>692</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7" t="s">
-        <v>603</v>
-      </c>
-      <c r="G95" s="10"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="7" t="s">
-        <v>847</v>
-      </c>
-      <c r="J95" s="10"/>
-      <c r="K95" s="10"/>
-      <c r="L95" s="7"/>
-      <c r="M95" s="7"/>
-    </row>
-    <row r="96" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A96" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>724</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>606</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>607</v>
-      </c>
-      <c r="I96" s="7" t="s">
-        <v>848</v>
-      </c>
-      <c r="J96" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K96" s="15" t="s">
-        <v>608</v>
-      </c>
-      <c r="L96" s="7"/>
-      <c r="M96" s="7" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A97" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>744</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7" t="s">
-        <v>611</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>612</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="I97" s="7" t="s">
-        <v>849</v>
-      </c>
-      <c r="J97" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="K97" s="15" t="s">
-        <v>614</v>
-      </c>
-      <c r="L97" s="7"/>
-      <c r="M97" s="9" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A98" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>717</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>619</v>
-      </c>
-      <c r="I98" s="7" t="s">
-        <v>850</v>
-      </c>
-      <c r="J98" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="K98" s="15" t="s">
-        <v>620</v>
-      </c>
-      <c r="L98" s="7"/>
-      <c r="M98" s="9" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A99" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7" t="s">
-        <v>623</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>624</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>625</v>
-      </c>
-      <c r="I99" s="7" t="s">
-        <v>851</v>
-      </c>
-      <c r="J99" s="10" t="s">
-        <v>562</v>
-      </c>
-      <c r="K99" s="15" t="s">
-        <v>626</v>
-      </c>
-      <c r="L99" s="7"/>
-      <c r="M99" s="9" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A100" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>628</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>695</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7" t="s">
-        <v>629</v>
-      </c>
-      <c r="G100" s="10"/>
-      <c r="H100" s="7"/>
-      <c r="I100" s="7" t="s">
-        <v>852</v>
-      </c>
-      <c r="J100" s="10"/>
-      <c r="K100" s="10"/>
-      <c r="L100" s="7"/>
-      <c r="M100" s="7"/>
-    </row>
-    <row r="101" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A101" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B101" s="7" t="s">
-        <v>630</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>694</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="10"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="J101" s="10"/>
-      <c r="K101" s="10"/>
-      <c r="L101" s="7"/>
-      <c r="M101" s="7"/>
-    </row>
-    <row r="102" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A102" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>631</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>694</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="10"/>
-      <c r="H102" s="7"/>
-      <c r="I102" s="7" t="s">
-        <v>632</v>
-      </c>
-      <c r="J102" s="10"/>
-      <c r="K102" s="10"/>
-      <c r="L102" s="7"/>
-      <c r="M102" s="7"/>
-    </row>
-    <row r="103" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A103" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>633</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>693</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
-      <c r="G103" s="10"/>
-      <c r="H103" s="7"/>
-      <c r="I103" s="7" t="s">
-        <v>634</v>
-      </c>
-      <c r="J103" s="10"/>
-      <c r="K103" s="10"/>
-      <c r="L103" s="7"/>
-      <c r="M103" s="7"/>
-    </row>
-    <row r="104" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A104" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>635</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>711</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7" t="s">
-        <v>636</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="H104" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="I104" s="7" t="s">
-        <v>854</v>
-      </c>
-      <c r="J104" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="K104" s="15" t="s">
-        <v>639</v>
-      </c>
-      <c r="L104" s="7"/>
-      <c r="M104" s="9" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" ht="85" x14ac:dyDescent="0.2">
-      <c r="A105" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="G105" s="10" t="s">
-        <v>643</v>
-      </c>
-      <c r="H105" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="I105" s="7" t="s">
-        <v>645</v>
-      </c>
-      <c r="J105" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K105" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="L105" s="7"/>
-      <c r="M105" s="9" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A106" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>648</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>781</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7" t="s">
-        <v>649</v>
-      </c>
-      <c r="G106" s="10"/>
-      <c r="H106" s="7"/>
-      <c r="J106" s="10"/>
-      <c r="K106" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="L106" s="7"/>
-      <c r="M106" s="7"/>
-    </row>
-    <row r="107" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A107" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>782</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="G107" s="10"/>
-      <c r="H107" s="7"/>
-      <c r="J107" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K107" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
-    </row>
-    <row r="108" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A108" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>654</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="G108" s="10"/>
-      <c r="H108" s="7"/>
-      <c r="J108" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K108" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
-    </row>
-    <row r="109" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A109" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>784</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="G109" s="10"/>
-      <c r="H109" s="7"/>
-      <c r="J109" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K109" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="L109" s="7"/>
-      <c r="M109" s="7"/>
-    </row>
-    <row r="110" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A110" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B110" s="7" t="s">
-        <v>656</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>785</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="G110" s="10"/>
-      <c r="H110" s="7"/>
-      <c r="J110" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K110" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="L110" s="7"/>
-      <c r="M110" s="7"/>
-    </row>
-    <row r="111" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A111" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>657</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="G111" s="10"/>
-      <c r="H111" s="7"/>
-      <c r="J111" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K111" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="L111" s="7"/>
-      <c r="M111" s="7"/>
-    </row>
-    <row r="112" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A112" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>658</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>787</v>
-      </c>
-      <c r="D112" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="G112" s="10"/>
-      <c r="H112" s="7"/>
-      <c r="J112" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K112" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="L112" s="7"/>
-      <c r="M112" s="7"/>
-    </row>
-    <row r="113" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A113" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>659</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>788</v>
-      </c>
-      <c r="D113" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="G113" s="10"/>
-      <c r="H113" s="7"/>
-      <c r="J113" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K113" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="L113" s="7"/>
-      <c r="M113" s="7"/>
-    </row>
-    <row r="114" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A114" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>660</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7" t="s">
-        <v>661</v>
-      </c>
-      <c r="G114" s="10"/>
-      <c r="H114" s="7"/>
-      <c r="J114" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="K114" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="L114" s="7"/>
-      <c r="M114" s="7"/>
-    </row>
-    <row r="115" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A115" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>662</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>790</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="G115" s="10"/>
-      <c r="H115" s="7"/>
-      <c r="J115" s="10" t="s">
-        <v>663</v>
-      </c>
-      <c r="K115" s="10" t="s">
-        <v>864</v>
-      </c>
-      <c r="L115" s="7"/>
-      <c r="M115" s="7"/>
-    </row>
-    <row r="116" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A116" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B116" s="7" t="s">
-        <v>664</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>791</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="G116" s="10"/>
-      <c r="H116" s="7"/>
-      <c r="J116" s="10" t="s">
-        <v>663</v>
-      </c>
-      <c r="K116" s="10" t="s">
-        <v>864</v>
-      </c>
-      <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
-    </row>
-    <row r="117" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A117" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>665</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>792</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="G117" s="10"/>
-      <c r="H117" s="7"/>
-      <c r="J117" s="10" t="s">
-        <v>663</v>
-      </c>
-      <c r="K117" s="10" t="s">
-        <v>864</v>
-      </c>
-      <c r="L117" s="7"/>
-      <c r="M117" s="7"/>
-    </row>
-    <row r="118" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A118" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>666</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>793</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E118" s="7"/>
-      <c r="F118" s="2" t="s">
-        <v>865</v>
-      </c>
-      <c r="G118" s="10" t="s">
-        <v>667</v>
-      </c>
-      <c r="H118" s="7" t="s">
-        <v>668</v>
-      </c>
-      <c r="I118" s="7" t="s">
-        <v>669</v>
-      </c>
-      <c r="J118" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>866</v>
-      </c>
-      <c r="L118" s="7"/>
-      <c r="M118" s="7"/>
-    </row>
-    <row r="119" spans="1:13" ht="119" x14ac:dyDescent="0.2">
-      <c r="A119" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>670</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>794</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="E119" s="7"/>
-      <c r="F119" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="G119" s="10"/>
-      <c r="H119" s="7" t="s">
-        <v>671</v>
-      </c>
-      <c r="I119" s="7" t="s">
+      <c r="K119" s="12" t="s">
         <v>672</v>
       </c>
-      <c r="J119" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="K119" s="15" t="s">
+      <c r="L119" s="7" t="s">
         <v>673</v>
       </c>
-      <c r="L119" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="M119" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9792,810 +9525,810 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B12" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B13" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B14" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B17" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B18" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B19" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B20" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B21" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B22" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B23" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B24" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B26" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B28" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B30" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B31" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B32" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B33" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B34" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B35" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B36" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B37" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B38" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B40" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B41" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B43" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B44" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B45" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B46" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B47" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B48" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B49" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B50" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B51" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B52" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B53" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B54" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B57" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B58" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B59" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B60" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B62" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>736</v>
+      </c>
+      <c r="B63" t="s">
         <v>737</v>
-      </c>
-      <c r="B63" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B64" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B65" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B66" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B67" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B68" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B69" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B71" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B72" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B73" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B74" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B75" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B76" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B77" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B78" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B79" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B80" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B81" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B82" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B83" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B84" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B85" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B86" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B87" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B88" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B89" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B91" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B92" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B93" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B95" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B96" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B97" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B98" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>773</v>
+      </c>
+      <c r="B99" t="s">
         <v>774</v>
-      </c>
-      <c r="B99" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B100" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B101" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
   </sheetData>
